--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Zličín/Databaze Zličín 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Zličín/Databaze Zličín 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5593" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5659" uniqueCount="370">
   <si>
     <t>Datum</t>
   </si>
@@ -450,6 +450,18 @@
     <t>10 min 49 s</t>
   </si>
   <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>10 min 07 s</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>10 min 48 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -1075,9 +1087,6 @@
   </si>
   <si>
     <t>Jana Lowe</t>
-  </si>
-  <si>
-    <t>10 min 48 s</t>
   </si>
   <si>
     <t>23.01.2026</t>
@@ -5664,6 +5673,420 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="M128" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O128" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M129" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="N129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O129" s="3">
+        <v>540.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P130" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="S130" s="3">
+        <v>12759.2</v>
+      </c>
+      <c r="T130" s="3">
+        <v>5534.0</v>
+      </c>
+      <c r="U130" s="3">
+        <v>8433.0</v>
+      </c>
+      <c r="V130" s="3">
+        <v>13899.0</v>
+      </c>
+      <c r="W130" s="3">
+        <v>483.0</v>
+      </c>
+      <c r="X130" s="3">
+        <v>753.0</v>
+      </c>
+      <c r="Y130" s="3">
+        <v>8001.0</v>
+      </c>
+      <c r="Z130" s="3">
+        <v>200.0</v>
+      </c>
+      <c r="AA130" s="3">
+        <v>760.0</v>
+      </c>
+      <c r="AB130" s="3">
+        <v>52041.2</v>
+      </c>
+      <c r="AC130" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AD130" s="3">
+        <v>0.24955078579180323</v>
+      </c>
+      <c r="AH130" s="3">
+        <v>1120.0</v>
+      </c>
+      <c r="AI130" s="3">
+        <v>855.0</v>
+      </c>
+      <c r="AJ130" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AK130" s="3">
+        <v>587.0</v>
+      </c>
+      <c r="AL130" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AM130" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AN130" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO130" s="3">
+        <v>121.0</v>
+      </c>
+      <c r="AP130" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="AQ130" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS130" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="AT130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU130" s="3">
+        <v>0.92</v>
+      </c>
+      <c r="AV130" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M134" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="N134" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O134" s="3">
+        <v>315.0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M135" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="N135" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O135" s="3">
+        <v>720.0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P136" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="S136" s="3">
+        <v>12090.0</v>
+      </c>
+      <c r="T136" s="3">
+        <v>2164.0</v>
+      </c>
+      <c r="U136" s="3">
+        <v>18090.0</v>
+      </c>
+      <c r="V136" s="3">
+        <v>16255.2</v>
+      </c>
+      <c r="W136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X136" s="3">
+        <v>1580.0</v>
+      </c>
+      <c r="Y136" s="3">
+        <v>3881.0</v>
+      </c>
+      <c r="AA136" s="3">
+        <v>2610.0</v>
+      </c>
+      <c r="AB136" s="3">
+        <v>56121.7</v>
+      </c>
+      <c r="AC136" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="AD136" s="3">
+        <v>0.266887523962182</v>
+      </c>
+      <c r="AI136" s="3">
+        <v>1035.0</v>
+      </c>
+      <c r="AJ136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL136" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="AM136" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AN136" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO136" s="3">
+        <v>134.0</v>
+      </c>
+      <c r="AP136" s="3">
+        <v>29.0</v>
+      </c>
+      <c r="AQ136" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS136" s="3">
+        <v>0.10344827586206896</v>
+      </c>
+      <c r="AT136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU136" s="3">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="AV136" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5824,7 +6247,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>106</v>
@@ -5844,7 +6267,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>106</v>
@@ -5864,7 +6287,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>106</v>
@@ -5884,7 +6307,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>106</v>
@@ -5904,7 +6327,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>106</v>
@@ -5924,7 +6347,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>106</v>
@@ -5953,7 +6376,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>106</v>
@@ -5982,7 +6405,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>106</v>
@@ -5999,7 +6422,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>106</v>
@@ -6053,7 +6476,7 @@
         <v>3.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN10" s="3">
         <v>2.0</v>
@@ -6085,7 +6508,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>109</v>
@@ -6105,7 +6528,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>109</v>
@@ -6125,7 +6548,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>109</v>
@@ -6145,7 +6568,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>109</v>
@@ -6165,7 +6588,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>109</v>
@@ -6194,7 +6617,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>109</v>
@@ -6223,7 +6646,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>109</v>
@@ -6312,7 +6735,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>49</v>
@@ -6332,7 +6755,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
@@ -6352,7 +6775,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
@@ -6364,7 +6787,7 @@
         <v>55</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>59</v>
@@ -6372,7 +6795,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -6381,7 +6804,7 @@
         <v>60</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>61</v>
@@ -6392,7 +6815,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -6412,7 +6835,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>49</v>
@@ -6432,7 +6855,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>49</v>
@@ -6461,7 +6884,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>49</v>
@@ -6490,7 +6913,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>49</v>
@@ -6519,7 +6942,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>49</v>
@@ -6548,7 +6971,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>49</v>
@@ -6602,7 +7025,7 @@
         <v>0.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AN28" s="3">
         <v>4.0</v>
@@ -6634,7 +7057,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>74</v>
@@ -6654,7 +7077,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>74</v>
@@ -6674,7 +7097,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>74</v>
@@ -6683,7 +7106,7 @@
         <v>60</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>61</v>
@@ -6694,7 +7117,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>74</v>
@@ -6723,7 +7146,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>74</v>
@@ -6752,7 +7175,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>74</v>
@@ -6781,7 +7204,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>74</v>
@@ -6838,7 +7261,7 @@
         <v>1.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN35" s="3">
         <v>3.0</v>
@@ -6870,7 +7293,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>87</v>
@@ -6890,7 +7313,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>87</v>
@@ -6899,7 +7322,7 @@
         <v>63</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>89</v>
@@ -6910,7 +7333,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>87</v>
@@ -6930,13 +7353,13 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>55</v>
@@ -6950,7 +7373,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>87</v>
@@ -6979,7 +7402,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>87</v>
@@ -7033,7 +7456,7 @@
         <v>0.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AN41" s="3">
         <v>1.0</v>
@@ -7065,7 +7488,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>96</v>
@@ -7085,7 +7508,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>96</v>
@@ -7105,7 +7528,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>96</v>
@@ -7125,7 +7548,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>96</v>
@@ -7134,7 +7557,7 @@
         <v>60</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>89</v>
@@ -7145,7 +7568,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>96</v>
@@ -7165,7 +7588,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>96</v>
@@ -7194,7 +7617,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>96</v>
@@ -7223,7 +7646,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>96</v>
@@ -7252,7 +7675,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>96</v>
@@ -7306,7 +7729,7 @@
         <v>0.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AN50" s="3">
         <v>3.0</v>
@@ -7338,7 +7761,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>102</v>
@@ -7353,12 +7776,12 @@
         <v>52</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>102</v>
@@ -7373,12 +7796,12 @@
         <v>89</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>102</v>
@@ -7398,7 +7821,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>102</v>
@@ -7427,7 +7850,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>102</v>
@@ -7456,7 +7879,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>102</v>
@@ -7510,7 +7933,7 @@
         <v>0.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AN56" s="3">
         <v>2.0</v>
@@ -7542,7 +7965,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>106</v>
@@ -7562,7 +7985,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>106</v>
@@ -7582,7 +8005,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>106</v>
@@ -7602,7 +8025,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>106</v>
@@ -7622,7 +8045,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>106</v>
@@ -7634,7 +8057,7 @@
         <v>70</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>62</v>
@@ -7651,7 +8074,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>106</v>
@@ -7680,7 +8103,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>106</v>
@@ -7737,7 +8160,7 @@
         <v>6.0</v>
       </c>
       <c r="AM63" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN63" s="3">
         <v>2.0</v>
@@ -7769,7 +8192,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>109</v>
@@ -7789,7 +8212,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>109</v>
@@ -7809,7 +8232,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>109</v>
@@ -7829,7 +8252,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>109</v>
@@ -7849,7 +8272,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>109</v>
@@ -7878,7 +8301,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>109</v>
@@ -7932,7 +8355,7 @@
         <v>0.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN69" s="3">
         <v>1.0</v>
@@ -7964,7 +8387,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>49</v>
@@ -7984,7 +8407,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>49</v>
@@ -8004,7 +8427,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>49</v>
@@ -8024,7 +8447,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>49</v>
@@ -8044,7 +8467,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>49</v>
@@ -8073,7 +8496,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>49</v>
@@ -8102,7 +8525,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>49</v>
@@ -8111,7 +8534,7 @@
         <v>98</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>68</v>
@@ -8131,7 +8554,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>49</v>
@@ -8160,7 +8583,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>49</v>
@@ -8220,7 +8643,7 @@
         <v>1.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AN78" s="3">
         <v>4.0</v>
@@ -8252,7 +8675,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>74</v>
@@ -8267,12 +8690,12 @@
         <v>68</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>74</v>
@@ -8292,7 +8715,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>74</v>
@@ -8312,7 +8735,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>74</v>
@@ -8341,7 +8764,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>74</v>
@@ -8353,10 +8776,10 @@
         <v>55</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M83" s="3">
         <v>7.0</v>
@@ -8370,7 +8793,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>74</v>
@@ -8385,7 +8808,7 @@
         <v>61</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M84" s="3">
         <v>7.0</v>
@@ -8399,7 +8822,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>74</v>
@@ -8453,7 +8876,7 @@
         <v>3.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AN85" s="3">
         <v>3.0</v>
@@ -8485,7 +8908,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>87</v>
@@ -8505,7 +8928,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>87</v>
@@ -8525,7 +8948,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>87</v>
@@ -8545,7 +8968,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>87</v>
@@ -8574,7 +8997,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>87</v>
@@ -8628,7 +9051,7 @@
         <v>2.0</v>
       </c>
       <c r="AM90" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AN90" s="3">
         <v>1.0</v>
@@ -8660,7 +9083,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>96</v>
@@ -8680,7 +9103,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>96</v>
@@ -8700,7 +9123,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>96</v>
@@ -8723,7 +9146,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>96</v>
@@ -8752,7 +9175,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>96</v>
@@ -8781,7 +9204,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>96</v>
@@ -8838,7 +9261,7 @@
         <v>2.0</v>
       </c>
       <c r="AM96" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AN96" s="3">
         <v>2.0</v>
@@ -8870,7 +9293,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>102</v>
@@ -8890,7 +9313,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>102</v>
@@ -8910,7 +9333,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>102</v>
@@ -8930,7 +9353,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>102</v>
@@ -8959,7 +9382,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>102</v>
@@ -8971,10 +9394,10 @@
         <v>75</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M101" s="3">
         <v>4.0</v>
@@ -8988,7 +9411,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>102</v>
@@ -9011,7 +9434,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>102</v>
@@ -9068,7 +9491,7 @@
         <v>6.0</v>
       </c>
       <c r="AM103" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AN103" s="3">
         <v>2.0</v>
@@ -9100,7 +9523,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>106</v>
@@ -9120,7 +9543,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>106</v>
@@ -9140,7 +9563,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>106</v>
@@ -9160,7 +9583,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>106</v>
@@ -9189,7 +9612,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>106</v>
@@ -9218,7 +9641,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>106</v>
@@ -9307,7 +9730,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>109</v>
@@ -9327,7 +9750,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>109</v>
@@ -9347,7 +9770,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>109</v>
@@ -9367,7 +9790,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>109</v>
@@ -9387,7 +9810,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>109</v>
@@ -9416,7 +9839,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>109</v>
@@ -9445,7 +9868,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>109</v>
@@ -9468,7 +9891,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>109</v>
@@ -9531,7 +9954,7 @@
         <v>1.0</v>
       </c>
       <c r="AM117" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AN117" s="3">
         <v>2.0</v>
@@ -9563,7 +9986,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
@@ -9575,7 +9998,7 @@
         <v>78</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>59</v>
@@ -9583,7 +10006,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>49</v>
@@ -9598,12 +10021,12 @@
         <v>55</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>49</v>
@@ -9612,7 +10035,7 @@
         <v>50</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>61</v>
@@ -9623,7 +10046,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>49</v>
@@ -9643,7 +10066,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>49</v>
@@ -9672,7 +10095,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>49</v>
@@ -9701,7 +10124,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>49</v>
@@ -9724,7 +10147,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>49</v>
@@ -9744,7 +10167,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>49</v>
@@ -9801,7 +10224,7 @@
         <v>0.0</v>
       </c>
       <c r="AM126" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AN126" s="3">
         <v>2.0</v>
@@ -9833,7 +10256,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>74</v>
@@ -9853,7 +10276,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>74</v>
@@ -9873,7 +10296,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>74</v>
@@ -9893,7 +10316,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>74</v>
@@ -9922,7 +10345,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>74</v>
@@ -9951,7 +10374,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>74</v>
@@ -9980,7 +10403,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>74</v>
@@ -10037,7 +10460,7 @@
         <v>2.0</v>
       </c>
       <c r="AM133" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AN133" s="3">
         <v>3.0</v>
@@ -10069,7 +10492,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>87</v>
@@ -10089,7 +10512,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>87</v>
@@ -10109,7 +10532,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>87</v>
@@ -10129,7 +10552,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>87</v>
@@ -10149,7 +10572,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>87</v>
@@ -10178,7 +10601,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>87</v>
@@ -10207,7 +10630,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>87</v>
@@ -10261,7 +10684,7 @@
         <v>2.0</v>
       </c>
       <c r="AM140" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN140" s="3">
         <v>2.0</v>
@@ -10293,7 +10716,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>96</v>
@@ -10313,7 +10736,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>96</v>
@@ -10333,7 +10756,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>96</v>
@@ -10353,7 +10776,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>96</v>
@@ -10382,7 +10805,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>96</v>
@@ -10411,7 +10834,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>96</v>
@@ -10465,7 +10888,7 @@
         <v>3.0</v>
       </c>
       <c r="AM146" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AN146" s="3">
         <v>2.0</v>
@@ -10497,7 +10920,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>102</v>
@@ -10517,7 +10940,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>102</v>
@@ -10537,7 +10960,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>102</v>
@@ -10557,7 +10980,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>102</v>
@@ -10586,7 +11009,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>102</v>
@@ -10615,7 +11038,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>102</v>
@@ -10638,7 +11061,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>102</v>
@@ -10695,7 +11118,7 @@
         <v>0.0</v>
       </c>
       <c r="AM153" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN153" s="3">
         <v>2.0</v>
@@ -10727,7 +11150,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>106</v>
@@ -10747,7 +11170,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>106</v>
@@ -10767,7 +11190,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>106</v>
@@ -10787,7 +11210,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>106</v>
@@ -10810,7 +11233,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>106</v>
@@ -10839,7 +11262,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>106</v>
@@ -10862,7 +11285,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>106</v>
@@ -10916,7 +11339,7 @@
         <v>0.0</v>
       </c>
       <c r="AM160" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AN160" s="3">
         <v>1.0</v>
@@ -10948,7 +11371,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>109</v>
@@ -10968,7 +11391,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>109</v>
@@ -10988,7 +11411,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>109</v>
@@ -11008,7 +11431,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>109</v>
@@ -11037,7 +11460,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>109</v>
@@ -11066,7 +11489,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>109</v>
@@ -11086,7 +11509,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>109</v>
@@ -11146,7 +11569,7 @@
         <v>4.0</v>
       </c>
       <c r="AM167" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AN167" s="3">
         <v>2.0</v>
@@ -11178,7 +11601,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>49</v>
@@ -11193,12 +11616,12 @@
         <v>52</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>49</v>
@@ -11218,7 +11641,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>49</v>
@@ -11238,7 +11661,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>49</v>
@@ -11258,7 +11681,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>49</v>
@@ -11278,7 +11701,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>49</v>
@@ -11298,7 +11721,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -11327,7 +11750,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>49</v>
@@ -11356,7 +11779,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>49</v>
@@ -11385,7 +11808,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>49</v>
@@ -11439,7 +11862,7 @@
         <v>2.0</v>
       </c>
       <c r="AM177" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN177" s="3">
         <v>3.0</v>
@@ -11471,7 +11894,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>74</v>
@@ -11491,7 +11914,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>74</v>
@@ -11511,7 +11934,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>74</v>
@@ -11520,7 +11943,7 @@
         <v>60</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>61</v>
@@ -11531,7 +11954,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>74</v>
@@ -11551,7 +11974,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>74</v>
@@ -11580,7 +12003,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>74</v>
@@ -11609,7 +12032,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>74</v>
@@ -11638,7 +12061,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>74</v>
@@ -11695,7 +12118,7 @@
         <v>0.0</v>
       </c>
       <c r="AM185" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AN185" s="3">
         <v>3.0</v>
@@ -11727,7 +12150,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>87</v>
@@ -11747,7 +12170,7 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>87</v>
@@ -11767,7 +12190,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>87</v>
@@ -11787,7 +12210,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>87</v>
@@ -11807,7 +12230,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>87</v>
@@ -11836,7 +12259,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>87</v>
@@ -11865,7 +12288,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>87</v>
@@ -11919,7 +12342,7 @@
         <v>0.0</v>
       </c>
       <c r="AM192" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AN192" s="3">
         <v>2.0</v>
@@ -11951,7 +12374,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>96</v>
@@ -11971,7 +12394,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>96</v>
@@ -11991,7 +12414,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>96</v>
@@ -12000,7 +12423,7 @@
         <v>63</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>123</v>
@@ -12011,7 +12434,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>96</v>
@@ -12031,7 +12454,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>96</v>
@@ -12060,7 +12483,7 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>96</v>
@@ -12089,7 +12512,7 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>96</v>
@@ -12146,7 +12569,7 @@
         <v>2.0</v>
       </c>
       <c r="AM199" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AN199" s="3">
         <v>2.0</v>
@@ -12178,7 +12601,7 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>102</v>
@@ -12198,7 +12621,7 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>102</v>
@@ -12218,7 +12641,7 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>102</v>
@@ -12247,7 +12670,7 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>102</v>
@@ -12276,7 +12699,7 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>102</v>
@@ -12362,7 +12785,7 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>106</v>
@@ -12382,7 +12805,7 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>106</v>
@@ -12402,7 +12825,7 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>106</v>
@@ -12422,7 +12845,7 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>106</v>
@@ -12451,7 +12874,7 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>106</v>
@@ -12466,7 +12889,7 @@
         <v>58</v>
       </c>
       <c r="L209" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="N209" s="1" t="b">
         <v>1</v>
@@ -12474,7 +12897,7 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>106</v>
@@ -12503,7 +12926,7 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>106</v>
@@ -12557,7 +12980,7 @@
         <v>2.0</v>
       </c>
       <c r="AM211" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN211" s="3">
         <v>2.0</v>
@@ -12589,7 +13012,7 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>109</v>
@@ -12609,7 +13032,7 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>109</v>
@@ -12629,7 +13052,7 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>109</v>
@@ -12649,7 +13072,7 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>109</v>
@@ -12678,7 +13101,7 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>109</v>
@@ -12707,7 +13130,7 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>109</v>
@@ -12764,7 +13187,7 @@
         <v>7.0</v>
       </c>
       <c r="AM217" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AN217" s="3">
         <v>2.0</v>
@@ -12954,7 +13377,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>87</v>
@@ -12974,7 +13397,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>87</v>
@@ -12994,7 +13417,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>87</v>
@@ -13014,7 +13437,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>87</v>
@@ -13043,7 +13466,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -13072,7 +13495,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>87</v>
@@ -13126,7 +13549,7 @@
         <v>5.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -13158,7 +13581,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>96</v>
@@ -13178,7 +13601,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>96</v>
@@ -13198,7 +13621,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>96</v>
@@ -13218,7 +13641,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>96</v>
@@ -13251,7 +13674,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>96</v>
@@ -13284,7 +13707,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>96</v>
@@ -13342,7 +13765,7 @@
         <v>1.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AN13" s="3">
         <v>2.0</v>
@@ -13374,7 +13797,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>102</v>
@@ -13394,7 +13817,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>102</v>
@@ -13414,7 +13837,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>102</v>
@@ -13423,7 +13846,7 @@
         <v>60</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>89</v>
@@ -13434,7 +13857,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>102</v>
@@ -13454,7 +13877,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>102</v>
@@ -13483,7 +13906,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>102</v>
@@ -13512,7 +13935,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>102</v>
@@ -13566,7 +13989,7 @@
         <v>2.0</v>
       </c>
       <c r="AM20" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AN20" s="3">
         <v>2.0</v>
@@ -13598,7 +14021,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>106</v>
@@ -13618,7 +14041,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>106</v>
@@ -13638,7 +14061,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>106</v>
@@ -13653,12 +14076,12 @@
         <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>106</v>
@@ -13678,7 +14101,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>106</v>
@@ -13707,7 +14130,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>106</v>
@@ -13736,7 +14159,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>106</v>
@@ -13793,7 +14216,7 @@
         <v>3.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AN27" s="3">
         <v>2.0</v>
@@ -13825,7 +14248,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>109</v>
@@ -13845,7 +14268,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>109</v>
@@ -13865,7 +14288,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>109</v>
@@ -13885,7 +14308,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>109</v>
@@ -13905,7 +14328,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>109</v>
@@ -13934,7 +14357,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>109</v>
@@ -13963,7 +14386,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>109</v>
@@ -14049,7 +14472,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -14069,7 +14492,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -14089,7 +14512,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -14109,7 +14532,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>49</v>
@@ -14129,7 +14552,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>49</v>
@@ -14149,7 +14572,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -14178,7 +14601,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
@@ -14207,7 +14630,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
@@ -14236,7 +14659,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>49</v>
@@ -14265,7 +14688,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>49</v>
@@ -14319,7 +14742,7 @@
         <v>1.0</v>
       </c>
       <c r="AM44" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AN44" s="3">
         <v>4.0</v>
@@ -14351,7 +14774,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>74</v>
@@ -14366,12 +14789,12 @@
         <v>88</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>74</v>
@@ -14391,7 +14814,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>74</v>
@@ -14411,7 +14834,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>74</v>
@@ -14431,7 +14854,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>74</v>
@@ -14460,7 +14883,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>74</v>
@@ -14489,7 +14912,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>74</v>
@@ -14518,7 +14941,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>74</v>
@@ -14575,7 +14998,7 @@
         <v>3.0</v>
       </c>
       <c r="AM52" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AN52" s="3">
         <v>3.0</v>
@@ -14607,7 +15030,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>87</v>
@@ -14627,7 +15050,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>87</v>
@@ -14647,7 +15070,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>87</v>
@@ -14667,7 +15090,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>87</v>
@@ -14696,7 +15119,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>87</v>
@@ -14708,10 +15131,10 @@
         <v>55</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M57" s="3">
         <v>7.0</v>
@@ -14725,7 +15148,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>87</v>
@@ -14782,7 +15205,7 @@
         <v>1.0</v>
       </c>
       <c r="AM58" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AN58" s="3">
         <v>2.0</v>
@@ -14814,7 +15237,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>96</v>
@@ -14834,7 +15257,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>96</v>
@@ -14854,7 +15277,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>96</v>
@@ -14874,7 +15297,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>96</v>
@@ -14903,7 +15326,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>96</v>
@@ -14915,7 +15338,7 @@
         <v>70</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>90</v>
@@ -14932,7 +15355,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>96</v>
@@ -14986,7 +15409,7 @@
         <v>2.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN64" s="3">
         <v>2.0</v>
@@ -15018,7 +15441,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>102</v>
@@ -15038,7 +15461,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>102</v>
@@ -15058,7 +15481,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>102</v>
@@ -15087,7 +15510,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>102</v>
@@ -15116,7 +15539,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>102</v>
@@ -15202,7 +15625,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>106</v>
@@ -15222,7 +15645,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>106</v>
@@ -15242,7 +15665,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>106</v>
@@ -15262,7 +15685,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>106</v>
@@ -15282,7 +15705,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>106</v>
@@ -15311,7 +15734,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>106</v>
@@ -15340,7 +15763,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>106</v>
@@ -15397,7 +15820,7 @@
         <v>4.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN76" s="3">
         <v>2.0</v>
@@ -15429,7 +15852,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>109</v>
@@ -15449,7 +15872,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>109</v>
@@ -15469,7 +15892,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>109</v>
@@ -15489,7 +15912,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>109</v>
@@ -15509,7 +15932,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>109</v>
@@ -15529,7 +15952,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>109</v>
@@ -15558,7 +15981,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>109</v>
@@ -15587,7 +16010,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>109</v>
@@ -15641,7 +16064,7 @@
         <v>4.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AN84" s="3">
         <v>2.0</v>
@@ -15673,7 +16096,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>49</v>
@@ -15693,7 +16116,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
@@ -15713,7 +16136,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -15733,7 +16156,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -15753,7 +16176,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -15773,7 +16196,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -15802,7 +16225,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -15831,7 +16254,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>49</v>
@@ -15860,7 +16283,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -15917,7 +16340,7 @@
         <v>7.0</v>
       </c>
       <c r="AM93" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="AN93" s="3">
         <v>3.0</v>
@@ -15949,7 +16372,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>74</v>
@@ -15969,7 +16392,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>74</v>
@@ -15989,7 +16412,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>74</v>
@@ -16009,7 +16432,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>74</v>
@@ -16029,7 +16452,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>74</v>
@@ -16049,7 +16472,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>74</v>
@@ -16078,7 +16501,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>74</v>
@@ -16107,7 +16530,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>74</v>
@@ -16136,7 +16559,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>74</v>
@@ -16190,7 +16613,7 @@
         <v>1.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AN102" s="3">
         <v>3.0</v>
@@ -16222,7 +16645,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>87</v>
@@ -16242,13 +16665,13 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>51</v>
@@ -16262,7 +16685,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>87</v>
@@ -16282,7 +16705,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>87</v>
@@ -16302,7 +16725,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>87</v>
@@ -16331,7 +16754,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>87</v>
@@ -16360,7 +16783,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>87</v>
@@ -16414,7 +16837,7 @@
         <v>3.0</v>
       </c>
       <c r="AM109" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AN109" s="3">
         <v>2.0</v>
@@ -16446,7 +16869,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>96</v>
@@ -16461,12 +16884,12 @@
         <v>52</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>96</v>
@@ -16486,7 +16909,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>96</v>
@@ -16506,7 +16929,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>96</v>
@@ -16535,7 +16958,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>96</v>
@@ -16564,7 +16987,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>96</v>
@@ -16621,7 +17044,7 @@
         <v>0.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN115" s="3">
         <v>2.0</v>
@@ -16653,7 +17076,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>102</v>
@@ -16673,7 +17096,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>102</v>
@@ -16693,7 +17116,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>102</v>
@@ -16713,7 +17136,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>102</v>
@@ -16742,7 +17165,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>102</v>
@@ -16771,7 +17194,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>102</v>
@@ -16834,7 +17257,7 @@
         <v>0.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AN121" s="3">
         <v>2.0</v>
@@ -16866,7 +17289,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>106</v>
@@ -16886,7 +17309,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>106</v>
@@ -16906,7 +17329,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>106</v>
@@ -16926,7 +17349,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>106</v>
@@ -16955,7 +17378,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>106</v>
@@ -16984,7 +17407,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>106</v>
@@ -17041,7 +17464,7 @@
         <v>1.0</v>
       </c>
       <c r="AM127" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AN127" s="3">
         <v>2.0</v>
@@ -17073,7 +17496,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>109</v>
@@ -17093,7 +17516,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>109</v>
@@ -17113,7 +17536,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>109</v>
@@ -17133,7 +17556,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>109</v>
@@ -17153,7 +17576,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>109</v>
@@ -17182,7 +17605,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>109</v>
@@ -17211,7 +17634,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>109</v>
@@ -17268,7 +17691,7 @@
         <v>2.0</v>
       </c>
       <c r="AM134" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AN134" s="3">
         <v>2.0</v>
@@ -17300,7 +17723,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>49</v>
@@ -17320,7 +17743,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>49</v>
@@ -17340,7 +17763,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>49</v>
@@ -17360,7 +17783,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>49</v>
@@ -17380,7 +17803,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>49</v>
@@ -17400,7 +17823,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>49</v>
@@ -17420,7 +17843,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>49</v>
@@ -17453,7 +17876,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>49</v>
@@ -17463,7 +17886,7 @@
       <c r="E142" s="1"/>
       <c r="G142" s="1"/>
       <c r="H142" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>55</v>
@@ -17486,7 +17909,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>49</v>
@@ -17519,7 +17942,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>49</v>
@@ -17552,7 +17975,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>49</v>
@@ -17613,7 +18036,7 @@
         <v>3.0</v>
       </c>
       <c r="AM145" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AN145" s="3">
         <v>4.0</v>
@@ -17645,7 +18068,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>74</v>
@@ -17665,7 +18088,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>74</v>
@@ -17685,7 +18108,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>74</v>
@@ -17705,7 +18128,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>74</v>
@@ -17725,7 +18148,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>74</v>
@@ -17745,7 +18168,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>74</v>
@@ -17774,7 +18197,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>74</v>
@@ -17803,7 +18226,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>74</v>
@@ -17832,7 +18255,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>74</v>
@@ -17886,7 +18309,7 @@
         <v>5.0</v>
       </c>
       <c r="AM154" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AN154" s="3">
         <v>3.0</v>
@@ -17918,7 +18341,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>87</v>
@@ -17938,7 +18361,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>87</v>
@@ -17958,7 +18381,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>87</v>
@@ -17978,7 +18401,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>87</v>
@@ -17998,13 +18421,13 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>70</v>
@@ -18027,7 +18450,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>87</v>
@@ -18056,7 +18479,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>87</v>
@@ -18068,10 +18491,10 @@
         <v>55</v>
       </c>
       <c r="J161" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M161" s="3">
         <v>4.0</v>
@@ -18085,7 +18508,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>87</v>
@@ -18142,7 +18565,7 @@
         <v>4.0</v>
       </c>
       <c r="AM162" s="1" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AN162" s="3">
         <v>3.0</v>
@@ -18174,7 +18597,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>96</v>
@@ -18194,7 +18617,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>96</v>
@@ -18214,7 +18637,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>96</v>
@@ -18234,7 +18657,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>96</v>
@@ -18263,7 +18686,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>96</v>
@@ -18292,7 +18715,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>96</v>
@@ -18346,7 +18769,7 @@
         <v>1.0</v>
       </c>
       <c r="AM168" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN168" s="3">
         <v>2.0</v>
@@ -18378,7 +18801,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>102</v>
@@ -18398,7 +18821,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>102</v>
@@ -18418,7 +18841,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>102</v>
@@ -18438,7 +18861,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>102</v>
@@ -18467,7 +18890,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>102</v>
@@ -18490,7 +18913,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>102</v>
@@ -18519,7 +18942,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>102</v>
@@ -18576,7 +18999,7 @@
         <v>2.0</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AN175" s="3">
         <v>2.0</v>
@@ -18608,7 +19031,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>106</v>
@@ -18628,7 +19051,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>106</v>
@@ -18648,7 +19071,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>106</v>
@@ -18668,7 +19091,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>106</v>
@@ -18697,7 +19120,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>106</v>
@@ -18726,7 +19149,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>106</v>
@@ -18780,7 +19203,7 @@
         <v>10.0</v>
       </c>
       <c r="AM181" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AN181" s="3">
         <v>2.0</v>
@@ -18812,7 +19235,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>109</v>
@@ -18827,12 +19250,12 @@
         <v>52</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>109</v>
@@ -18852,7 +19275,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>109</v>
@@ -18872,7 +19295,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>109</v>
@@ -18892,7 +19315,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>109</v>
@@ -18907,7 +19330,7 @@
         <v>138</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M186" s="3">
         <v>6.0</v>
@@ -18921,7 +19344,7 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>109</v>
@@ -18950,7 +19373,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>109</v>
@@ -18979,7 +19402,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>109</v>
@@ -19036,7 +19459,7 @@
         <v>4.0</v>
       </c>
       <c r="AM189" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AN189" s="3">
         <v>3.0</v>
@@ -19068,7 +19491,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>49</v>
@@ -19088,7 +19511,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>49</v>
@@ -19108,7 +19531,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>49</v>
@@ -19128,7 +19551,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>49</v>
@@ -19157,7 +19580,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>49</v>
@@ -19180,7 +19603,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>49</v>
@@ -19209,7 +19632,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>49</v>
@@ -19238,7 +19661,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>49</v>
@@ -19295,7 +19718,7 @@
         <v>5.0</v>
       </c>
       <c r="AM197" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AN197" s="3">
         <v>3.0</v>
@@ -19327,7 +19750,7 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>74</v>
@@ -19342,12 +19765,12 @@
         <v>61</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>74</v>
@@ -19367,7 +19790,7 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>74</v>
@@ -19387,7 +19810,7 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>74</v>
@@ -19407,7 +19830,7 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>74</v>
@@ -19436,7 +19859,7 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>74</v>
@@ -19465,7 +19888,7 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>74</v>
@@ -19477,10 +19900,10 @@
         <v>55</v>
       </c>
       <c r="J204" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L204" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M204" s="3">
         <v>7.0</v>
@@ -19494,7 +19917,7 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>74</v>
@@ -19551,7 +19974,7 @@
         <v>2.0</v>
       </c>
       <c r="AM205" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AN205" s="3">
         <v>3.0</v>
@@ -19583,7 +20006,7 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>87</v>
@@ -19603,7 +20026,7 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>87</v>
@@ -19623,7 +20046,7 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>87</v>
@@ -19643,7 +20066,7 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>87</v>
@@ -19663,7 +20086,7 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>87</v>
@@ -19692,7 +20115,7 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>87</v>
@@ -19721,7 +20144,7 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>87</v>
@@ -19807,7 +20230,7 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>96</v>
@@ -19827,7 +20250,7 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>96</v>
@@ -19847,7 +20270,7 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>96</v>
@@ -19876,7 +20299,7 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>96</v>
@@ -19905,7 +20328,7 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>96</v>
@@ -19959,7 +20382,7 @@
         <v>3.0</v>
       </c>
       <c r="AM217" s="1" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AN217" s="3">
         <v>2.0</v>
@@ -19991,7 +20414,7 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>102</v>
@@ -20011,7 +20434,7 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>102</v>
@@ -20031,7 +20454,7 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>102</v>
@@ -20040,7 +20463,7 @@
         <v>60</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>61</v>
@@ -20051,7 +20474,7 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>102</v>
@@ -20080,7 +20503,7 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>102</v>
@@ -20109,7 +20532,7 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>102</v>
@@ -20169,7 +20592,7 @@
         <v>0.0</v>
       </c>
       <c r="AM223" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AN223" s="3">
         <v>2.0</v>
@@ -20359,7 +20782,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>87</v>
@@ -20379,7 +20802,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>87</v>
@@ -20399,7 +20822,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>87</v>
@@ -20419,7 +20842,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>87</v>
@@ -20448,7 +20871,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>87</v>
@@ -20477,7 +20900,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>87</v>
@@ -20531,7 +20954,7 @@
         <v>0.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -20563,7 +20986,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>96</v>
@@ -20583,7 +21006,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>96</v>
@@ -20603,7 +21026,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>96</v>
@@ -20623,7 +21046,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>96</v>
@@ -20652,7 +21075,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>96</v>
@@ -20681,7 +21104,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>96</v>
@@ -20735,7 +21158,7 @@
         <v>5.0</v>
       </c>
       <c r="AM13" s="1" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AN13" s="3">
         <v>2.0</v>
@@ -20767,7 +21190,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>102</v>
@@ -20787,7 +21210,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>102</v>
@@ -20807,7 +21230,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>102</v>
@@ -20827,7 +21250,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>102</v>
@@ -20856,7 +21279,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>102</v>
@@ -20885,7 +21308,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>102</v>
@@ -20939,7 +21362,7 @@
         <v>0.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AN19" s="3">
         <v>2.0</v>
@@ -20971,7 +21394,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>106</v>
@@ -20991,7 +21414,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>106</v>
@@ -21011,7 +21434,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>106</v>
@@ -21031,7 +21454,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>106</v>
@@ -21051,7 +21474,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>106</v>
@@ -21080,7 +21503,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>106</v>
@@ -21109,7 +21532,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>106</v>
@@ -21138,7 +21561,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>106</v>
@@ -21192,7 +21615,7 @@
         <v>1.0</v>
       </c>
       <c r="AM27" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN27" s="3">
         <v>3.0</v>
@@ -21224,7 +21647,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>109</v>
@@ -21244,7 +21667,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>109</v>
@@ -21264,7 +21687,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>109</v>
@@ -21284,7 +21707,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>109</v>
@@ -21299,12 +21722,12 @@
         <v>89</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>109</v>
@@ -21333,7 +21756,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>109</v>
@@ -21362,7 +21785,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>109</v>
@@ -21371,13 +21794,13 @@
         <v>66</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>93</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M34" s="3">
         <v>8.0</v>
@@ -21391,7 +21814,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>109</v>
@@ -21448,7 +21871,7 @@
         <v>3.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AN35" s="3">
         <v>3.0</v>
@@ -21480,7 +21903,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -21500,7 +21923,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -21520,7 +21943,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>49</v>
@@ -21540,7 +21963,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>49</v>
@@ -21560,7 +21983,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -21572,10 +21995,10 @@
         <v>70</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="M40" s="3">
         <v>9.0</v>
@@ -21589,7 +22012,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
@@ -21618,7 +22041,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
@@ -21627,7 +22050,7 @@
         <v>66</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>68</v>
@@ -21647,7 +22070,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>49</v>
@@ -21704,7 +22127,7 @@
         <v>8.0</v>
       </c>
       <c r="AM43" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN43" s="3">
         <v>3.0</v>
@@ -21736,7 +22159,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>74</v>
@@ -21756,7 +22179,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>74</v>
@@ -21776,7 +22199,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>74</v>
@@ -21796,13 +22219,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>55</v>
@@ -21816,7 +22239,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>74</v>
@@ -21845,7 +22268,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>74</v>
@@ -21874,7 +22297,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>74</v>
@@ -21903,7 +22326,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>74</v>
@@ -21989,7 +22412,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>87</v>
@@ -22009,13 +22432,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>51</v>
@@ -22029,7 +22452,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>87</v>
@@ -22049,7 +22472,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>87</v>
@@ -22069,13 +22492,13 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>55</v>
@@ -22098,7 +22521,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>87</v>
@@ -22127,7 +22550,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>87</v>
@@ -22213,7 +22636,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>96</v>
@@ -22233,7 +22656,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>96</v>
@@ -22253,7 +22676,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>96</v>
@@ -22262,7 +22685,7 @@
         <v>60</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>89</v>
@@ -22273,7 +22696,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>96</v>
@@ -22302,7 +22725,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>96</v>
@@ -22331,7 +22754,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>96</v>
@@ -22388,7 +22811,7 @@
         <v>2.0</v>
       </c>
       <c r="AM64" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AN64" s="3">
         <v>2.0</v>
@@ -22420,7 +22843,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>102</v>
@@ -22440,7 +22863,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>102</v>
@@ -22460,7 +22883,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>102</v>
@@ -22480,7 +22903,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>102</v>
@@ -22509,7 +22932,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>102</v>
@@ -22538,7 +22961,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>102</v>
@@ -22595,7 +23018,7 @@
         <v>1.0</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AN70" s="3">
         <v>2.0</v>
@@ -22627,7 +23050,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>106</v>
@@ -22642,12 +23065,12 @@
         <v>52</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>106</v>
@@ -22667,7 +23090,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>106</v>
@@ -22687,7 +23110,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>106</v>
@@ -22716,7 +23139,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>106</v>
@@ -22745,7 +23168,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>106</v>
@@ -22774,7 +23197,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>106</v>
@@ -22828,7 +23251,7 @@
         <v>2.0</v>
       </c>
       <c r="AM77" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AN77" s="3">
         <v>3.0</v>
@@ -22860,7 +23283,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>109</v>
@@ -22880,7 +23303,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>109</v>
@@ -22900,7 +23323,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>109</v>
@@ -22920,7 +23343,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>109</v>
@@ -22940,7 +23363,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>109</v>
@@ -22969,7 +23392,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>109</v>
@@ -22998,7 +23421,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>109</v>
@@ -23027,7 +23450,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>109</v>
@@ -23113,7 +23536,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
@@ -23133,7 +23556,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -23153,7 +23576,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>49</v>
@@ -23173,7 +23596,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>49</v>
@@ -23193,7 +23616,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>49</v>
@@ -23213,7 +23636,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>49</v>
@@ -23242,7 +23665,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>49</v>
@@ -23271,7 +23694,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -23300,7 +23723,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -23354,7 +23777,7 @@
         <v>29.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AN94" s="3">
         <v>3.0</v>
@@ -23386,7 +23809,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>74</v>
@@ -23406,7 +23829,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>74</v>
@@ -23415,7 +23838,7 @@
         <v>57</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>61</v>
@@ -23426,7 +23849,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>74</v>
@@ -23446,7 +23869,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>74</v>
@@ -23466,7 +23889,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>74</v>
@@ -23486,7 +23909,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>74</v>
@@ -23515,7 +23938,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>74</v>
@@ -23544,7 +23967,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>74</v>
@@ -23601,7 +24024,7 @@
         <v>1.0</v>
       </c>
       <c r="AM102" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="AN102" s="3">
         <v>2.0</v>
@@ -23633,7 +24056,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>87</v>
@@ -23653,7 +24076,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>87</v>
@@ -23673,7 +24096,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>87</v>
@@ -23693,7 +24116,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>87</v>
@@ -23713,7 +24136,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>87</v>
@@ -23742,7 +24165,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>87</v>
@@ -23796,7 +24219,7 @@
         <v>0.0</v>
       </c>
       <c r="AM108" s="1" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AN108" s="3">
         <v>1.0</v>
@@ -23828,7 +24251,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>96</v>
@@ -23848,7 +24271,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>96</v>
@@ -23868,7 +24291,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>96</v>
@@ -23888,7 +24311,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>96</v>
@@ -23897,7 +24320,7 @@
         <v>60</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>93</v>
@@ -23908,7 +24331,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>96</v>
@@ -23937,7 +24360,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>96</v>
@@ -23966,7 +24389,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>96</v>
@@ -24023,7 +24446,7 @@
         <v>0.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AN115" s="3">
         <v>2.0</v>
@@ -24055,7 +24478,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>102</v>
@@ -24075,7 +24498,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>102</v>
@@ -24095,7 +24518,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>102</v>
@@ -24110,7 +24533,7 @@
         <v>138</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M118" s="3">
         <v>5.0</v>
@@ -24124,7 +24547,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>102</v>
@@ -24153,7 +24576,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>102</v>
@@ -24182,7 +24605,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>102</v>
@@ -24242,7 +24665,7 @@
         <v>3.0</v>
       </c>
       <c r="AM121" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN121" s="3">
         <v>3.0</v>
@@ -24274,7 +24697,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>106</v>
@@ -24294,7 +24717,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>106</v>
@@ -24314,7 +24737,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>106</v>
@@ -24334,7 +24757,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>106</v>
@@ -24363,7 +24786,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>106</v>
@@ -24392,7 +24815,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>106</v>
@@ -24421,7 +24844,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>106</v>
@@ -24478,7 +24901,7 @@
         <v>1.0</v>
       </c>
       <c r="AM128" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AN128" s="3">
         <v>3.0</v>
@@ -24510,7 +24933,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>109</v>
@@ -24530,7 +24953,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>109</v>
@@ -24550,7 +24973,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>109</v>
@@ -24570,7 +24993,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>109</v>
@@ -24590,7 +25013,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>109</v>
@@ -24610,7 +25033,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>109</v>
@@ -24639,7 +25062,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>109</v>
@@ -24668,7 +25091,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>109</v>
@@ -24722,7 +25145,7 @@
         <v>1.0</v>
       </c>
       <c r="AM136" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AN136" s="3">
         <v>2.0</v>
@@ -24754,7 +25177,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>49</v>
@@ -24774,7 +25197,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>49</v>
@@ -24794,7 +25217,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>49</v>
@@ -24814,7 +25237,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>49</v>
@@ -24834,7 +25257,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>49</v>
@@ -24854,7 +25277,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>49</v>
@@ -24883,7 +25306,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>49</v>
@@ -24912,7 +25335,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>49</v>
@@ -24941,7 +25364,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>49</v>
@@ -24998,7 +25421,7 @@
         <v>4.0</v>
       </c>
       <c r="AM145" s="1" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="AN145" s="3">
         <v>3.0</v>
@@ -25030,7 +25453,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>74</v>
@@ -25050,7 +25473,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>74</v>
@@ -25070,7 +25493,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>74</v>
@@ -25090,7 +25513,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>74</v>
@@ -25102,7 +25525,7 @@
         <v>70</v>
       </c>
       <c r="J149" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="L149" s="2" t="s">
         <v>62</v>
@@ -25119,7 +25542,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>74</v>
@@ -25148,7 +25571,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>74</v>
@@ -25177,7 +25600,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>74</v>
@@ -25231,7 +25654,7 @@
         <v>0.0</v>
       </c>
       <c r="AM152" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AN152" s="3">
         <v>3.0</v>
@@ -25263,7 +25686,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>87</v>
@@ -25283,7 +25706,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>87</v>
@@ -25303,7 +25726,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>87</v>
@@ -25323,7 +25746,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>87</v>
@@ -25343,7 +25766,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>87</v>
@@ -25372,7 +25795,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>87</v>
@@ -25401,7 +25824,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>87</v>
@@ -25458,7 +25881,7 @@
         <v>1.0</v>
       </c>
       <c r="AM159" s="1" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AN159" s="3">
         <v>2.0</v>
@@ -25490,7 +25913,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>96</v>
@@ -25510,7 +25933,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>96</v>
@@ -25530,7 +25953,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>96</v>
@@ -25550,7 +25973,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>96</v>
@@ -25570,7 +25993,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>96</v>
@@ -25599,7 +26022,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>96</v>
@@ -25628,7 +26051,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>96</v>
@@ -25682,7 +26105,7 @@
         <v>5.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="AN166" s="3">
         <v>2.0</v>
@@ -25714,7 +26137,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>102</v>
@@ -25734,7 +26157,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>102</v>
@@ -25754,7 +26177,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>102</v>
@@ -25774,7 +26197,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>102</v>
@@ -25803,7 +26226,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>102</v>
@@ -25832,7 +26255,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>102</v>
@@ -25861,7 +26284,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>102</v>
@@ -25915,7 +26338,7 @@
         <v>4.0</v>
       </c>
       <c r="AM173" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AN173" s="3">
         <v>3.0</v>
@@ -25947,7 +26370,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>106</v>
@@ -25967,7 +26390,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>106</v>
@@ -25987,7 +26410,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>106</v>
@@ -26007,7 +26430,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>106</v>
@@ -26019,7 +26442,7 @@
         <v>70</v>
       </c>
       <c r="J177" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L177" s="2" t="s">
         <v>90</v>
@@ -26036,7 +26459,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>106</v>
@@ -26065,7 +26488,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>106</v>
@@ -26122,7 +26545,7 @@
         <v>4.0</v>
       </c>
       <c r="AM179" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AN179" s="3">
         <v>2.0</v>
@@ -26154,7 +26577,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>109</v>
@@ -26174,7 +26597,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>109</v>
@@ -26194,7 +26617,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>109</v>
@@ -26214,7 +26637,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>109</v>
@@ -26234,7 +26657,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>109</v>
@@ -26263,7 +26686,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>109</v>
@@ -26349,7 +26772,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>49</v>
@@ -26364,12 +26787,12 @@
         <v>52</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>49</v>
@@ -26389,7 +26812,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>49</v>
@@ -26409,7 +26832,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>49</v>
@@ -26429,7 +26852,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>49</v>
@@ -26441,7 +26864,7 @@
         <v>51</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>130</v>
@@ -26449,7 +26872,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>49</v>
@@ -26464,12 +26887,12 @@
         <v>61</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>49</v>
@@ -26498,7 +26921,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>49</v>
@@ -26527,7 +26950,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>49</v>
@@ -26556,7 +26979,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>49</v>
@@ -26610,7 +27033,7 @@
         <v>4.0</v>
       </c>
       <c r="AM195" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN195" s="3">
         <v>3.0</v>
@@ -26642,7 +27065,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>74</v>
@@ -26662,7 +27085,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>74</v>
@@ -26682,7 +27105,7 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>74</v>
@@ -26702,7 +27125,7 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>74</v>
@@ -26722,7 +27145,7 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>74</v>
@@ -26751,7 +27174,7 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>74</v>
@@ -26780,7 +27203,7 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>74</v>
@@ -26809,7 +27232,7 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>74</v>
@@ -26863,7 +27286,7 @@
         <v>0.0</v>
       </c>
       <c r="AM203" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AN203" s="3">
         <v>3.0</v>
@@ -27053,13 +27476,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
@@ -27073,7 +27496,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>109</v>
@@ -27093,7 +27516,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>109</v>
@@ -27113,7 +27536,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>109</v>
@@ -27133,7 +27556,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>109</v>
@@ -27153,13 +27576,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>55</v>
@@ -27173,7 +27596,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>109</v>
@@ -27202,13 +27625,13 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>109</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>55</v>
@@ -27231,7 +27654,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>109</v>
@@ -27291,7 +27714,7 @@
         <v>6.0</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AN10" s="3">
         <v>2.0</v>
@@ -27323,7 +27746,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -27343,7 +27766,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -27363,7 +27786,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
@@ -27383,7 +27806,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -27403,7 +27826,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -27423,7 +27846,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -27452,7 +27875,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -27506,7 +27929,7 @@
         <v>5.0</v>
       </c>
       <c r="AM17" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AN17" s="3">
         <v>1.0</v>
@@ -27538,7 +27961,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>74</v>
@@ -27558,7 +27981,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>74</v>
@@ -27570,7 +27993,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>78</v>
@@ -27578,7 +28001,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>74</v>
@@ -27598,7 +28021,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>74</v>
@@ -27618,7 +28041,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>74</v>
@@ -27647,7 +28070,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>74</v>
@@ -27710,7 +28133,7 @@
         <v>0.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AN23" s="3">
         <v>1.0</v>
@@ -27742,7 +28165,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>87</v>
@@ -27762,7 +28185,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>87</v>
@@ -27782,7 +28205,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>87</v>
@@ -27791,7 +28214,7 @@
         <v>60</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>89</v>
@@ -27802,7 +28225,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>87</v>
@@ -27831,7 +28254,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>87</v>
@@ -27888,7 +28311,7 @@
         <v>2.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AN28" s="3">
         <v>1.0</v>
@@ -27920,7 +28343,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>96</v>
@@ -27940,7 +28363,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>96</v>
@@ -27960,7 +28383,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>96</v>
@@ -27980,7 +28403,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>96</v>
@@ -28009,7 +28432,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>96</v>
@@ -28038,7 +28461,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>96</v>
@@ -28092,7 +28515,7 @@
         <v>2.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AN34" s="3">
         <v>2.0</v>
@@ -28124,7 +28547,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>102</v>
@@ -28144,7 +28567,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>102</v>
@@ -28164,7 +28587,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>102</v>
@@ -28193,7 +28616,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>102</v>
@@ -28247,7 +28670,7 @@
         <v>4.0</v>
       </c>
       <c r="AM38" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AN38" s="3">
         <v>1.0</v>
@@ -28279,7 +28702,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>106</v>
@@ -28288,18 +28711,18 @@
         <v>63</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>93</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>106</v>
@@ -28311,15 +28734,15 @@
         <v>51</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>106</v>
@@ -28339,7 +28762,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>106</v>
@@ -28359,7 +28782,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>106</v>
@@ -28388,7 +28811,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>106</v>
@@ -28417,7 +28840,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>106</v>
@@ -28474,7 +28897,7 @@
         <v>1.0</v>
       </c>
       <c r="AM45" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN45" s="3">
         <v>2.0</v>
@@ -28506,7 +28929,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>109</v>
@@ -28526,7 +28949,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>109</v>
@@ -28546,7 +28969,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>109</v>
@@ -28566,7 +28989,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>109</v>
@@ -28623,7 +29046,7 @@
         <v>1.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN49" s="3">
         <v>0.0</v>
@@ -28655,7 +29078,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>49</v>
@@ -28675,7 +29098,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>49</v>
@@ -28695,7 +29118,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>49</v>
@@ -28715,7 +29138,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>49</v>
@@ -28735,7 +29158,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>49</v>
@@ -28764,7 +29187,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>49</v>
@@ -28821,7 +29244,7 @@
         <v>20.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AN55" s="3">
         <v>1.0</v>
@@ -28853,7 +29276,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>74</v>
@@ -28862,18 +29285,18 @@
         <v>63</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>74</v>
@@ -28893,7 +29316,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>74</v>
@@ -28913,13 +29336,13 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>55</v>
@@ -28933,7 +29356,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>74</v>
@@ -28948,12 +29371,12 @@
         <v>61</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>74</v>
@@ -28973,7 +29396,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>74</v>
@@ -28983,7 +29406,7 @@
       <c r="E62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>55</v>
@@ -29006,7 +29429,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>74</v>
@@ -29064,7 +29487,7 @@
         <v>10.0</v>
       </c>
       <c r="AM63" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AN63" s="3">
         <v>1.0</v>
@@ -29096,7 +29519,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>87</v>
@@ -29116,7 +29539,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>87</v>
@@ -29136,7 +29559,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>87</v>
@@ -29156,7 +29579,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>87</v>
@@ -29185,7 +29608,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>87</v>
@@ -29242,7 +29665,7 @@
         <v>2.0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN68" s="3">
         <v>1.0</v>
@@ -29274,7 +29697,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>96</v>
@@ -29294,7 +29717,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>96</v>
@@ -29314,7 +29737,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>96</v>
@@ -29334,7 +29757,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>96</v>
@@ -29363,7 +29786,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>96</v>
@@ -29420,7 +29843,7 @@
         <v>5.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="AN73" s="3">
         <v>1.0</v>
@@ -29452,7 +29875,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>102</v>
@@ -29472,7 +29895,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>102</v>
@@ -29492,7 +29915,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>102</v>
@@ -29512,7 +29935,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>102</v>
@@ -29541,7 +29964,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>102</v>
@@ -29601,7 +30024,7 @@
         <v>0.0</v>
       </c>
       <c r="AM78" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN78" s="3">
         <v>1.0</v>
@@ -29633,7 +30056,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>106</v>
@@ -29653,7 +30076,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>106</v>
@@ -29673,7 +30096,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>106</v>
@@ -29693,7 +30116,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>106</v>
@@ -29705,7 +30128,7 @@
         <v>51</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>62</v>
@@ -29713,7 +30136,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>106</v>
@@ -29725,7 +30148,7 @@
         <v>70</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>90</v>
@@ -29742,7 +30165,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>106</v>
@@ -29771,7 +30194,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>106</v>
@@ -29825,7 +30248,7 @@
         <v>3.0</v>
       </c>
       <c r="AM85" s="1" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AN85" s="3">
         <v>2.0</v>
@@ -29857,7 +30280,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>109</v>
@@ -29877,7 +30300,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>109</v>
@@ -29897,7 +30320,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>109</v>
@@ -29917,7 +30340,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>109</v>
@@ -29937,7 +30360,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>109</v>
@@ -29957,7 +30380,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>109</v>
@@ -29986,7 +30409,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>109</v>
@@ -30043,7 +30466,7 @@
         <v>0.0</v>
       </c>
       <c r="AM92" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN92" s="3">
         <v>1.0</v>
@@ -30075,7 +30498,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>49</v>
@@ -30095,7 +30518,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>49</v>
@@ -30115,7 +30538,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>49</v>
@@ -30135,7 +30558,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>49</v>
@@ -30155,7 +30578,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>49</v>
@@ -30175,7 +30598,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -30204,13 +30627,13 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>55</v>
@@ -30233,7 +30656,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>49</v>
@@ -30290,7 +30713,7 @@
         <v>4.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AN100" s="3">
         <v>2.0</v>
@@ -30322,7 +30745,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>74</v>
@@ -30342,7 +30765,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>74</v>
@@ -30362,7 +30785,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>74</v>
@@ -30382,7 +30805,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>74</v>
@@ -30402,7 +30825,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>74</v>
@@ -30431,7 +30854,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>74</v>
@@ -30488,7 +30911,7 @@
         <v>5.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -30520,7 +30943,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>87</v>
@@ -30540,7 +30963,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>87</v>
@@ -30560,7 +30983,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>87</v>
@@ -30580,7 +31003,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>87</v>
@@ -30600,7 +31023,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>87</v>
@@ -30629,7 +31052,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>87</v>
@@ -30686,7 +31109,7 @@
         <v>4.0</v>
       </c>
       <c r="AM112" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AN112" s="3">
         <v>1.0</v>
@@ -30718,7 +31141,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>96</v>
@@ -30738,7 +31161,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>96</v>
@@ -30758,7 +31181,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>96</v>
@@ -30778,7 +31201,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>96</v>
@@ -30807,7 +31230,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>96</v>
@@ -30836,7 +31259,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>96</v>
@@ -30893,7 +31316,7 @@
         <v>0.0</v>
       </c>
       <c r="AM118" s="1" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="AN118" s="3">
         <v>2.0</v>
@@ -30925,7 +31348,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>102</v>
@@ -30945,7 +31368,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>102</v>
@@ -30965,7 +31388,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>102</v>
@@ -30985,7 +31408,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>102</v>
@@ -31014,7 +31437,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>102</v>
@@ -31074,7 +31497,7 @@
         <v>1.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AN123" s="3">
         <v>1.0</v>
@@ -31106,7 +31529,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>106</v>
@@ -31126,7 +31549,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>106</v>
@@ -31146,7 +31569,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>106</v>
@@ -31166,7 +31589,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>106</v>
@@ -31195,7 +31618,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>106</v>
@@ -31224,7 +31647,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>106</v>
@@ -31284,7 +31707,7 @@
         <v>3.0</v>
       </c>
       <c r="AM129" s="1" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AN129" s="3">
         <v>2.0</v>
@@ -31316,7 +31739,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>109</v>
@@ -31336,7 +31759,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>109</v>
@@ -31356,7 +31779,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>109</v>
@@ -31376,7 +31799,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>109</v>
@@ -31396,7 +31819,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>109</v>
@@ -31425,13 +31848,13 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>109</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>70</v>
@@ -31454,7 +31877,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>109</v>
@@ -31511,7 +31934,7 @@
         <v>1.0</v>
       </c>
       <c r="AM136" s="1" t="s">
-        <v>353</v>
+        <v>147</v>
       </c>
       <c r="AN136" s="3">
         <v>2.0</v>
@@ -31543,7 +31966,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>49</v>
@@ -31563,7 +31986,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>49</v>
@@ -31583,7 +32006,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>49</v>
@@ -31603,7 +32026,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>49</v>
@@ -31623,7 +32046,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>49</v>
@@ -31652,13 +32075,13 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="I142" s="2" t="s">
         <v>70</v>
@@ -31681,13 +32104,13 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I143" s="2" t="s">
         <v>55</v>
@@ -31710,7 +32133,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>49</v>
@@ -31767,7 +32190,7 @@
         <v>7.0</v>
       </c>
       <c r="AM144" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AN144" s="3">
         <v>3.0</v>
@@ -31799,7 +32222,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>74</v>
@@ -31814,12 +32237,12 @@
         <v>61</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>74</v>
@@ -31839,7 +32262,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>74</v>
@@ -31859,13 +32282,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>55</v>
@@ -31879,7 +32302,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>74</v>
@@ -31908,13 +32331,13 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I150" s="2" t="s">
         <v>55</v>
@@ -31937,13 +32360,13 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="I151" s="2" t="s">
         <v>55</v>
@@ -31966,7 +32389,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>74</v>
@@ -32026,7 +32449,7 @@
         <v>3.0</v>
       </c>
       <c r="AM152" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AN152" s="3">
         <v>3.0</v>
@@ -32058,7 +32481,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>87</v>
@@ -32078,7 +32501,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>87</v>
@@ -32098,7 +32521,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>87</v>
@@ -32118,7 +32541,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>87</v>
@@ -32138,7 +32561,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>87</v>
@@ -32167,13 +32590,13 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I158" s="2" t="s">
         <v>55</v>
@@ -32196,13 +32619,13 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>87</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>70</v>
@@ -32225,7 +32648,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>87</v>
@@ -32285,7 +32708,7 @@
         <v>4.0</v>
       </c>
       <c r="AM160" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AN160" s="3">
         <v>3.0</v>
@@ -32317,7 +32740,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>96</v>
@@ -32337,7 +32760,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>96</v>
@@ -32357,7 +32780,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>96</v>
@@ -32386,7 +32809,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>96</v>
@@ -32415,7 +32838,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>96</v>
@@ -32469,7 +32892,7 @@
         <v>0.0</v>
       </c>
       <c r="AM165" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AN165" s="3">
         <v>2.0</v>
@@ -32501,7 +32924,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>102</v>
@@ -32521,7 +32944,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>102</v>
@@ -32541,7 +32964,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>102</v>
@@ -32561,7 +32984,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>102</v>
@@ -32590,7 +33013,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>102</v>
@@ -32644,7 +33067,7 @@
         <v>0.0</v>
       </c>
       <c r="AM170" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AN170" s="3">
         <v>1.0</v>
@@ -32676,7 +33099,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>106</v>
@@ -32696,7 +33119,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>106</v>
@@ -32716,7 +33139,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>106</v>
@@ -32736,7 +33159,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>106</v>
@@ -32756,7 +33179,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>106</v>
@@ -32785,7 +33208,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>106</v>
@@ -32814,7 +33237,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>106</v>
@@ -32871,7 +33294,7 @@
         <v>0.0</v>
       </c>
       <c r="AM177" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AN177" s="3">
         <v>2.0</v>
@@ -32903,7 +33326,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>109</v>
@@ -32923,7 +33346,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>109</v>
@@ -32943,7 +33366,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>109</v>
@@ -32963,7 +33386,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>109</v>
@@ -32972,7 +33395,7 @@
         <v>60</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>89</v>
@@ -32983,7 +33406,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>109</v>
@@ -33012,7 +33435,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>109</v>
@@ -33041,7 +33464,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>109</v>
@@ -33127,7 +33550,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>49</v>
@@ -33147,7 +33570,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>49</v>
@@ -33167,7 +33590,7 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>49</v>
@@ -33187,7 +33610,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>49</v>
@@ -33207,7 +33630,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>49</v>
@@ -33219,7 +33642,7 @@
         <v>55</v>
       </c>
       <c r="J189" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L189" s="2" t="s">
         <v>59</v>
@@ -33236,7 +33659,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>49</v>
@@ -33265,7 +33688,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>49</v>
@@ -33294,7 +33717,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>49</v>
@@ -33317,7 +33740,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>49</v>
@@ -33374,7 +33797,7 @@
         <v>9.0</v>
       </c>
       <c r="AM193" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AN193" s="3">
         <v>3.0</v>
@@ -33406,7 +33829,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>74</v>
@@ -33426,7 +33849,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>74</v>
@@ -33446,7 +33869,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>74</v>
@@ -33466,7 +33889,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>74</v>
@@ -33495,7 +33918,7 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>74</v>
@@ -33524,7 +33947,7 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>74</v>
@@ -33553,7 +33976,7 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>74</v>
